--- a/synthetic/output/products/products.xlsx
+++ b/synthetic/output/products/products.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>product code</t>
+          <t>drug code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>therapeutic area</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -451,16 +451,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TemporaCare 1</t>
+          <t>FugitCare 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>766.89</v>
+        <v>1790.97</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -476,16 +476,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MaioresCare 2</t>
+          <t>TemporeCare 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2397.31</v>
+        <v>1687.03</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -501,16 +501,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DoloremCare 3</t>
+          <t>VoluptasCare 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>345.3</v>
+        <v>2464.53</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -526,16 +526,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MaximeCare 4</t>
+          <t>QuosCare 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>332.12</v>
+        <v>2179.56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -551,16 +551,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LiberoCare 5</t>
+          <t>EstCare 5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1548.94</v>
+        <v>767.14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EosCare 6</t>
+          <t>VitaeCare 6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1851.36</v>
+        <v>490.37</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -601,16 +601,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VelitCare 7</t>
+          <t>ItaqueCare 7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2435.48</v>
+        <v>602.8200000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FugiatCare 8</t>
+          <t>AspernaturCare 8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>289.12</v>
+        <v>1784.37</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -651,16 +651,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VoluptatesCare 9</t>
+          <t>EumCare 9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Diabetes</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2090.57</v>
+        <v>1561.91</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -676,16 +676,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VeroCare 10</t>
+          <t>AliquidCare 10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1485.65</v>
+        <v>1381.94</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -701,16 +701,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TeneturCare 11</t>
+          <t>IpsamCare 11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>209.98</v>
+        <v>492.17</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -726,16 +726,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AutCare 12</t>
+          <t>NatusCare 12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1955.36</v>
+        <v>747.87</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SequiCare 13</t>
+          <t>FugiatCare 13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2152.76</v>
+        <v>1743.07</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -776,16 +776,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TemporaCare 14</t>
+          <t>AtCare 14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1012.3</v>
+        <v>649.72</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -801,16 +801,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DoloresCare 15</t>
+          <t>ErrorCare 15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Antibiotic</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1625.64</v>
+        <v>2032.11</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QuibusdamCare 16</t>
+          <t>ReiciendisCare 16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>490.37</v>
+        <v>742.58</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -851,16 +851,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ExercitationemCare 17</t>
+          <t>IpsamCare 17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>602.8200000000001</v>
+        <v>2291.53</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -876,16 +876,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DoloremCare 18</t>
+          <t>ErrorCare 18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1784.37</v>
+        <v>610.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -901,16 +901,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OfficiisCare 19</t>
+          <t>UllamCare 19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Antibiotic</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1561.91</v>
+        <v>1049.52</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -926,16 +926,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ModiCare 20</t>
+          <t>PraesentiumCare 20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Antibiotic</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1381.94</v>
+        <v>442.89</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -951,16 +951,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FugitCare 21</t>
+          <t>NamCare 21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>492.17</v>
+        <v>691.91</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TemporeCare 22</t>
+          <t>TemporibusCare 22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>747.87</v>
+        <v>1892.83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1001,16 +1001,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VoluptasCare 23</t>
+          <t>OfficiaCare 23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1743.07</v>
+        <v>2254.77</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1026,16 +1026,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QuosCare 24</t>
+          <t>DictaCare 24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>649.72</v>
+        <v>968.79</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1051,16 +1051,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EstCare 25</t>
+          <t>FugaCare 25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2032.11</v>
+        <v>1322.86</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1076,16 +1076,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VitaeCare 26</t>
+          <t>DeseruntCare 26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Diabetes</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>742.58</v>
+        <v>1913.88</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ItaqueCare 27</t>
+          <t>ExpeditaCare 27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Diabetes</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2291.53</v>
+        <v>466.82</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1126,16 +1126,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AspernaturCare 28</t>
+          <t>RationeCare 28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>610.3</v>
+        <v>2000.99</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1151,16 +1151,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EumCare 29</t>
+          <t>QuidemCare 29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Antibiotic</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1049.52</v>
+        <v>1531.38</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AliquidCare 30</t>
+          <t>FugaCare 30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Antibiotic</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>442.89</v>
+        <v>1015.89</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>

--- a/synthetic/output/products/products.xlsx
+++ b/synthetic/output/products/products.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>therapeutic area</t>
+          <t>product category</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -451,16 +451,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FugitCare 1</t>
+          <t>RemCare 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1790.97</v>
+        <v>1944.64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -476,16 +476,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TemporeCare 2</t>
+          <t>RepellatCare 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1687.03</v>
+        <v>367.73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -501,16 +501,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VoluptasCare 3</t>
+          <t>PariaturCare 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2464.53</v>
+        <v>479.58</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -526,16 +526,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QuosCare 4</t>
+          <t>ExercitationemCare 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2179.56</v>
+        <v>2389.16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -551,16 +551,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EstCare 5</t>
+          <t>PariaturCare 5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>767.14</v>
+        <v>2432.53</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VitaeCare 6</t>
+          <t>NemoCare 6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>490.37</v>
+        <v>1318.44</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -601,16 +601,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ItaqueCare 7</t>
+          <t>EaqueCare 7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Diabetes</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>602.8200000000001</v>
+        <v>2189.24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AspernaturCare 8</t>
+          <t>ConsequaturCare 8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1784.37</v>
+        <v>2120.01</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -651,16 +651,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EumCare 9</t>
+          <t>ConsequaturCare 9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1561.91</v>
+        <v>466.81</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AliquidCare 10</t>
+          <t>UndeCare 10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1381.94</v>
+        <v>1394.51</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -701,16 +701,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IpsamCare 11</t>
+          <t>NonCare 11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>492.17</v>
+        <v>1537.47</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -726,16 +726,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NatusCare 12</t>
+          <t>LiberoCare 12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Antibiotic</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>747.87</v>
+        <v>146.74</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FugiatCare 13</t>
+          <t>NisiCare 13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1743.07</v>
+        <v>2208.93</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -776,16 +776,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AtCare 14</t>
+          <t>NequeCare 14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>649.72</v>
+        <v>674.6900000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -801,16 +801,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ErrorCare 15</t>
+          <t>OmnisCare 15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2032.11</v>
+        <v>2207.22</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ReiciendisCare 16</t>
+          <t>AsperioresCare 16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Diabetes</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>742.58</v>
+        <v>305.57</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -851,16 +851,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IpsamCare 17</t>
+          <t>VeniamCare 17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Antibiotic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2291.53</v>
+        <v>2058.46</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -876,16 +876,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ErrorCare 18</t>
+          <t>UllamCare 18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>610.3</v>
+        <v>408.14</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UllamCare 19</t>
+          <t>TeneturCare 19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1049.52</v>
+        <v>2372.44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -926,16 +926,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PraesentiumCare 20</t>
+          <t>ConsequunturCare 20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Antibiotic</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>442.89</v>
+        <v>736.14</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -951,16 +951,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NamCare 21</t>
+          <t>AssumendaCare 21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>691.91</v>
+        <v>2414.47</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TemporibusCare 22</t>
+          <t>NecessitatibusCare 22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1892.83</v>
+        <v>1811.08</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OfficiaCare 23</t>
+          <t>LaboreCare 23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2254.77</v>
+        <v>2488.36</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1026,16 +1026,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DictaCare 24</t>
+          <t>CorruptiCare 24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>968.79</v>
+        <v>1151.44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1051,16 +1051,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FugaCare 25</t>
+          <t>ExpeditaCare 25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Antibiotic</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1322.86</v>
+        <v>390.41</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1076,16 +1076,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DeseruntCare 26</t>
+          <t>EarumCare 26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1913.88</v>
+        <v>253.66</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ExpeditaCare 27</t>
+          <t>EaqueCare 27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>466.82</v>
+        <v>1511.94</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1126,16 +1126,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RationeCare 28</t>
+          <t>QuidemCare 28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2000.99</v>
+        <v>1512.26</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1151,16 +1151,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>QuidemCare 29</t>
+          <t>OccaecatiCare 29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1531.38</v>
+        <v>270.38</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FugaCare 30</t>
+          <t>DeseruntCare 30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1015.89</v>
+        <v>649.46</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
